--- a/foo.xlsx
+++ b/foo.xlsx
@@ -438,19 +438,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -458,19 +458,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -498,19 +498,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -518,16 +518,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -538,19 +538,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -558,19 +558,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -578,19 +578,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -601,16 +601,16 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -618,19 +618,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
